--- a/src/technology/pv-residential-large/pv-residential-large.xlsx
+++ b/src/technology/pv-residential-large/pv-residential-large.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhanes\GitHub\tyche\src\technology\pv-residential-large\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7675BF1C-6985-477F-9037-D0E9EFA624BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E265FD-F354-4D2F-A1A9-5289D3E64FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="6" xr2:uid="{919693B4-77B5-41B5-AA55-4D3552FB964A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="743" activeTab="7" xr2:uid="{919693B4-77B5-41B5-AA55-4D3552FB964A}"/>
   </bookViews>
   <sheets>
     <sheet name="designs" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,12 @@
     <sheet name="parameters" sheetId="5" r:id="rId5"/>
     <sheet name="results" sheetId="6" r:id="rId6"/>
     <sheet name="tranches" sheetId="7" r:id="rId7"/>
+    <sheet name="metadata" sheetId="8" r:id="rId8"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">designs!$A$1:$G$300</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">parameters!$A$1:$G$553</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5119" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5160" uniqueCount="289">
   <si>
     <t>Category</t>
   </si>
@@ -882,6 +887,33 @@
   </si>
   <si>
     <t>st.triang(0.5, loc=675, scale=500)</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Maximum funding amounts are decided during scenario development in collaboration with the decision-maker.</t>
+  </si>
+  <si>
+    <t>Invest in the Module R&amp;D category to lower module costs for manufacturing, purchase and installation costs, and operating and maintenance, and to increase module lifetime and efficiency.</t>
+  </si>
+  <si>
+    <t>Invest in the Inverter R&amp;D category to lower inverter costs for manufacturing, installation, and operation; to increase inverter lifetime and efficiency; and to improve inverter reliability.</t>
+  </si>
+  <si>
+    <t>Invest in the BoS (Balance of Systems) R&amp;D category to reduce BoS purchase and installation costs and to increase the lifetime of BoS components.</t>
+  </si>
+  <si>
+    <t>Reduction in levelized cost of energy relative to the "No R&amp;D" base case. Maximizing this metric will find solutions that offer the greatest cost savings to consumers.</t>
+  </si>
+  <si>
+    <t>Reduction in cradle-to-installation life cycle GHGs relative to the "No R&amp;D" base case. Maximizing this metric will find solutions that offer the greatest emissions reductions to manufacturers.</t>
+  </si>
+  <si>
+    <t>Investment Amounts</t>
   </si>
 </sst>
 </file>
@@ -938,9 +970,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -978,7 +1010,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1084,7 +1116,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1226,7 +1258,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1235,12 +1267,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{070FB04D-2C74-445D-8DA3-54633B601228}">
   <dimension ref="A1:G300"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -1263,7 +1301,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -1286,7 +1324,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -1309,7 +1347,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -1332,7 +1370,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -1355,7 +1393,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -1378,7 +1416,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -1398,7 +1436,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -1421,7 +1459,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -1444,7 +1482,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -1467,7 +1505,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -1490,7 +1528,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -1513,7 +1551,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -1536,7 +1574,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1559,7 +1597,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -1582,7 +1620,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1605,7 +1643,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1628,7 +1666,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1651,7 +1689,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -1674,7 +1712,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -1694,7 +1732,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -1717,7 +1755,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -1740,7 +1778,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -1763,7 +1801,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -1786,7 +1824,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -1809,7 +1847,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -1832,7 +1870,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -1855,7 +1893,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1878,7 +1916,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1901,7 +1939,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -1924,7 +1962,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -1947,7 +1985,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -1970,7 +2008,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -1990,7 +2028,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -2013,7 +2051,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -2036,7 +2074,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -2059,7 +2097,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -2082,7 +2120,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -2105,7 +2143,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -2128,7 +2166,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -2151,7 +2189,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -2174,7 +2212,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -2197,7 +2235,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>40</v>
       </c>
@@ -2220,7 +2258,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>40</v>
       </c>
@@ -2243,7 +2281,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>40</v>
       </c>
@@ -2266,7 +2304,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>40</v>
       </c>
@@ -2286,7 +2324,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>40</v>
       </c>
@@ -2309,7 +2347,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>40</v>
       </c>
@@ -2332,7 +2370,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>40</v>
       </c>
@@ -2355,7 +2393,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>40</v>
       </c>
@@ -2378,7 +2416,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>40</v>
       </c>
@@ -2401,7 +2439,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>40</v>
       </c>
@@ -2424,7 +2462,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>40</v>
       </c>
@@ -2447,7 +2485,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>40</v>
       </c>
@@ -2470,7 +2508,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>40</v>
       </c>
@@ -2493,7 +2531,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>40</v>
       </c>
@@ -2516,7 +2554,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>40</v>
       </c>
@@ -2539,7 +2577,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>40</v>
       </c>
@@ -2562,7 +2600,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>40</v>
       </c>
@@ -2582,7 +2620,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>40</v>
       </c>
@@ -2605,7 +2643,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>40</v>
       </c>
@@ -2628,7 +2666,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>40</v>
       </c>
@@ -2651,7 +2689,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>40</v>
       </c>
@@ -2674,7 +2712,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>40</v>
       </c>
@@ -2697,7 +2735,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>40</v>
       </c>
@@ -2720,7 +2758,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>40</v>
       </c>
@@ -2743,7 +2781,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>40</v>
       </c>
@@ -2766,7 +2804,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>40</v>
       </c>
@@ -2789,7 +2827,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>40</v>
       </c>
@@ -2812,7 +2850,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>40</v>
       </c>
@@ -2835,7 +2873,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>40</v>
       </c>
@@ -2858,7 +2896,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>40</v>
       </c>
@@ -2878,7 +2916,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>40</v>
       </c>
@@ -2901,7 +2939,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>40</v>
       </c>
@@ -2924,7 +2962,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>40</v>
       </c>
@@ -2947,7 +2985,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>40</v>
       </c>
@@ -2970,7 +3008,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>40</v>
       </c>
@@ -2993,7 +3031,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>40</v>
       </c>
@@ -3016,7 +3054,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>40</v>
       </c>
@@ -3039,7 +3077,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>40</v>
       </c>
@@ -3062,7 +3100,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>40</v>
       </c>
@@ -3085,7 +3123,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>40</v>
       </c>
@@ -3108,7 +3146,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>40</v>
       </c>
@@ -3131,7 +3169,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>40</v>
       </c>
@@ -3154,7 +3192,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>40</v>
       </c>
@@ -3174,7 +3212,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>40</v>
       </c>
@@ -3197,7 +3235,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>40</v>
       </c>
@@ -3220,7 +3258,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>40</v>
       </c>
@@ -3243,7 +3281,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>40</v>
       </c>
@@ -3266,7 +3304,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>40</v>
       </c>
@@ -3289,7 +3327,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>40</v>
       </c>
@@ -3312,7 +3350,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>40</v>
       </c>
@@ -3335,7 +3373,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>40</v>
       </c>
@@ -3358,7 +3396,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>40</v>
       </c>
@@ -3381,7 +3419,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>40</v>
       </c>
@@ -3404,7 +3442,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>40</v>
       </c>
@@ -3427,7 +3465,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>40</v>
       </c>
@@ -3450,7 +3488,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>40</v>
       </c>
@@ -3470,7 +3508,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>40</v>
       </c>
@@ -3493,7 +3531,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>40</v>
       </c>
@@ -3516,7 +3554,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>40</v>
       </c>
@@ -3539,7 +3577,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>40</v>
       </c>
@@ -3562,7 +3600,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>40</v>
       </c>
@@ -3585,7 +3623,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>40</v>
       </c>
@@ -3608,7 +3646,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>40</v>
       </c>
@@ -3631,7 +3669,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>40</v>
       </c>
@@ -3654,7 +3692,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>40</v>
       </c>
@@ -3677,7 +3715,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>40</v>
       </c>
@@ -3700,7 +3738,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>40</v>
       </c>
@@ -3723,7 +3761,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>40</v>
       </c>
@@ -3746,7 +3784,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>40</v>
       </c>
@@ -3766,7 +3804,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>40</v>
       </c>
@@ -3789,7 +3827,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>40</v>
       </c>
@@ -3812,7 +3850,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>40</v>
       </c>
@@ -3835,7 +3873,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>40</v>
       </c>
@@ -3858,7 +3896,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>40</v>
       </c>
@@ -3881,7 +3919,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>40</v>
       </c>
@@ -3904,7 +3942,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>40</v>
       </c>
@@ -3927,7 +3965,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>40</v>
       </c>
@@ -3950,7 +3988,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>40</v>
       </c>
@@ -3973,7 +4011,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>40</v>
       </c>
@@ -3996,7 +4034,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>40</v>
       </c>
@@ -4019,7 +4057,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>40</v>
       </c>
@@ -4042,7 +4080,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>40</v>
       </c>
@@ -4062,7 +4100,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>40</v>
       </c>
@@ -4085,7 +4123,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>40</v>
       </c>
@@ -4108,7 +4146,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>40</v>
       </c>
@@ -4131,7 +4169,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>40</v>
       </c>
@@ -4154,7 +4192,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>40</v>
       </c>
@@ -4177,7 +4215,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>40</v>
       </c>
@@ -4200,7 +4238,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>40</v>
       </c>
@@ -4223,7 +4261,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>40</v>
       </c>
@@ -4246,7 +4284,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>40</v>
       </c>
@@ -4269,7 +4307,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>40</v>
       </c>
@@ -4292,7 +4330,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>40</v>
       </c>
@@ -4315,7 +4353,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>40</v>
       </c>
@@ -4338,7 +4376,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>40</v>
       </c>
@@ -4358,7 +4396,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>40</v>
       </c>
@@ -4381,7 +4419,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>40</v>
       </c>
@@ -4404,7 +4442,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>40</v>
       </c>
@@ -4427,7 +4465,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>40</v>
       </c>
@@ -4450,7 +4488,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>40</v>
       </c>
@@ -4473,7 +4511,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>40</v>
       </c>
@@ -4496,7 +4534,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>40</v>
       </c>
@@ -4519,7 +4557,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>40</v>
       </c>
@@ -4542,7 +4580,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>40</v>
       </c>
@@ -4565,7 +4603,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>40</v>
       </c>
@@ -4588,7 +4626,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>40</v>
       </c>
@@ -4611,7 +4649,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>40</v>
       </c>
@@ -4634,7 +4672,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>40</v>
       </c>
@@ -4654,7 +4692,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>40</v>
       </c>
@@ -4677,7 +4715,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>40</v>
       </c>
@@ -4700,7 +4738,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>40</v>
       </c>
@@ -4723,7 +4761,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>40</v>
       </c>
@@ -4746,7 +4784,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>40</v>
       </c>
@@ -4769,7 +4807,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>40</v>
       </c>
@@ -4792,7 +4830,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>40</v>
       </c>
@@ -4815,7 +4853,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>40</v>
       </c>
@@ -4838,7 +4876,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>40</v>
       </c>
@@ -4861,7 +4899,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>40</v>
       </c>
@@ -4884,7 +4922,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>40</v>
       </c>
@@ -4907,7 +4945,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>40</v>
       </c>
@@ -4930,7 +4968,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>40</v>
       </c>
@@ -4950,7 +4988,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>40</v>
       </c>
@@ -4973,7 +5011,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>40</v>
       </c>
@@ -4996,7 +5034,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>40</v>
       </c>
@@ -5019,7 +5057,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>40</v>
       </c>
@@ -5042,7 +5080,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>40</v>
       </c>
@@ -5065,7 +5103,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>40</v>
       </c>
@@ -5088,7 +5126,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>40</v>
       </c>
@@ -5111,7 +5149,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>40</v>
       </c>
@@ -5134,7 +5172,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>40</v>
       </c>
@@ -5157,7 +5195,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>40</v>
       </c>
@@ -5180,7 +5218,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>40</v>
       </c>
@@ -5203,7 +5241,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>40</v>
       </c>
@@ -5226,7 +5264,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>40</v>
       </c>
@@ -5246,7 +5284,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>40</v>
       </c>
@@ -5269,7 +5307,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>40</v>
       </c>
@@ -5292,7 +5330,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>40</v>
       </c>
@@ -5315,7 +5353,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>40</v>
       </c>
@@ -5338,7 +5376,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>40</v>
       </c>
@@ -5361,7 +5399,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>40</v>
       </c>
@@ -5384,7 +5422,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>40</v>
       </c>
@@ -5407,7 +5445,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>40</v>
       </c>
@@ -5430,7 +5468,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>40</v>
       </c>
@@ -5453,7 +5491,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>40</v>
       </c>
@@ -5476,7 +5514,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>40</v>
       </c>
@@ -5499,7 +5537,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>40</v>
       </c>
@@ -5522,7 +5560,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>40</v>
       </c>
@@ -5542,7 +5580,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>40</v>
       </c>
@@ -5565,7 +5603,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>40</v>
       </c>
@@ -5588,7 +5626,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>40</v>
       </c>
@@ -5611,7 +5649,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>40</v>
       </c>
@@ -5634,7 +5672,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>40</v>
       </c>
@@ -5657,7 +5695,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>40</v>
       </c>
@@ -5680,7 +5718,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>40</v>
       </c>
@@ -5703,7 +5741,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>40</v>
       </c>
@@ -5726,7 +5764,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>40</v>
       </c>
@@ -5749,7 +5787,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>40</v>
       </c>
@@ -5772,7 +5810,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>40</v>
       </c>
@@ -5795,7 +5833,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>40</v>
       </c>
@@ -5818,7 +5856,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>40</v>
       </c>
@@ -5838,7 +5876,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>40</v>
       </c>
@@ -5861,7 +5899,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>40</v>
       </c>
@@ -5884,7 +5922,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>40</v>
       </c>
@@ -5907,7 +5945,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>40</v>
       </c>
@@ -5930,7 +5968,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>40</v>
       </c>
@@ -5953,7 +5991,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>40</v>
       </c>
@@ -5976,7 +6014,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>40</v>
       </c>
@@ -5999,7 +6037,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>40</v>
       </c>
@@ -6022,7 +6060,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>40</v>
       </c>
@@ -6045,7 +6083,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>40</v>
       </c>
@@ -6068,7 +6106,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>40</v>
       </c>
@@ -6091,7 +6129,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>40</v>
       </c>
@@ -6114,7 +6152,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>40</v>
       </c>
@@ -6134,7 +6172,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>40</v>
       </c>
@@ -6157,7 +6195,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>40</v>
       </c>
@@ -6180,7 +6218,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>40</v>
       </c>
@@ -6203,7 +6241,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>40</v>
       </c>
@@ -6226,7 +6264,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>40</v>
       </c>
@@ -6249,7 +6287,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>40</v>
       </c>
@@ -6272,7 +6310,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>40</v>
       </c>
@@ -6295,7 +6333,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>40</v>
       </c>
@@ -6318,7 +6356,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>40</v>
       </c>
@@ -6341,7 +6379,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>40</v>
       </c>
@@ -6364,7 +6402,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>40</v>
       </c>
@@ -6387,7 +6425,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>40</v>
       </c>
@@ -6410,7 +6448,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>40</v>
       </c>
@@ -6430,7 +6468,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>40</v>
       </c>
@@ -6453,7 +6491,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>40</v>
       </c>
@@ -6476,7 +6514,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>40</v>
       </c>
@@ -6499,7 +6537,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>40</v>
       </c>
@@ -6522,7 +6560,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>40</v>
       </c>
@@ -6545,7 +6583,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>40</v>
       </c>
@@ -6568,7 +6606,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>40</v>
       </c>
@@ -6591,7 +6629,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>40</v>
       </c>
@@ -6614,7 +6652,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>40</v>
       </c>
@@ -6637,7 +6675,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>40</v>
       </c>
@@ -6660,7 +6698,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>40</v>
       </c>
@@ -6683,7 +6721,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>40</v>
       </c>
@@ -6706,7 +6744,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>40</v>
       </c>
@@ -6726,7 +6764,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>40</v>
       </c>
@@ -6749,7 +6787,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>40</v>
       </c>
@@ -6772,7 +6810,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>40</v>
       </c>
@@ -6795,7 +6833,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>40</v>
       </c>
@@ -6818,7 +6856,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>40</v>
       </c>
@@ -6841,7 +6879,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>40</v>
       </c>
@@ -6864,7 +6902,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>40</v>
       </c>
@@ -6887,7 +6925,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>40</v>
       </c>
@@ -6910,7 +6948,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>40</v>
       </c>
@@ -6933,7 +6971,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>40</v>
       </c>
@@ -6956,7 +6994,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>40</v>
       </c>
@@ -6979,7 +7017,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>40</v>
       </c>
@@ -7002,7 +7040,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>40</v>
       </c>
@@ -7022,7 +7060,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>40</v>
       </c>
@@ -7045,7 +7083,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>40</v>
       </c>
@@ -7068,7 +7106,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>40</v>
       </c>
@@ -7091,7 +7129,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>40</v>
       </c>
@@ -7114,7 +7152,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>40</v>
       </c>
@@ -7137,7 +7175,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>40</v>
       </c>
@@ -7160,7 +7198,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>40</v>
       </c>
@@ -7183,7 +7221,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>40</v>
       </c>
@@ -7206,7 +7244,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>40</v>
       </c>
@@ -7229,7 +7267,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>40</v>
       </c>
@@ -7252,7 +7290,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>40</v>
       </c>
@@ -7275,7 +7313,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>40</v>
       </c>
@@ -7298,7 +7336,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>40</v>
       </c>
@@ -7318,7 +7356,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>40</v>
       </c>
@@ -7341,7 +7379,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>40</v>
       </c>
@@ -7364,7 +7402,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>40</v>
       </c>
@@ -7387,7 +7425,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>40</v>
       </c>
@@ -7410,7 +7448,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>40</v>
       </c>
@@ -7433,7 +7471,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>40</v>
       </c>
@@ -7456,7 +7494,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>40</v>
       </c>
@@ -7479,7 +7517,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>40</v>
       </c>
@@ -7502,7 +7540,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>40</v>
       </c>
@@ -7525,7 +7563,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>40</v>
       </c>
@@ -7548,7 +7586,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>40</v>
       </c>
@@ -7571,7 +7609,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>40</v>
       </c>
@@ -7594,7 +7632,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>40</v>
       </c>
@@ -7614,7 +7652,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>40</v>
       </c>
@@ -7637,7 +7675,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>40</v>
       </c>
@@ -7660,7 +7698,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>40</v>
       </c>
@@ -7683,7 +7721,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>40</v>
       </c>
@@ -7706,7 +7744,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>40</v>
       </c>
@@ -7729,7 +7767,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>40</v>
       </c>
@@ -7752,7 +7790,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>40</v>
       </c>
@@ -7775,7 +7813,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>40</v>
       </c>
@@ -7798,7 +7836,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>40</v>
       </c>
@@ -7821,7 +7859,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>40</v>
       </c>
@@ -7844,7 +7882,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>40</v>
       </c>
@@ -7867,7 +7905,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>40</v>
       </c>
@@ -7890,7 +7928,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>40</v>
       </c>
@@ -7910,7 +7948,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>40</v>
       </c>
@@ -7933,7 +7971,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>40</v>
       </c>
@@ -7956,7 +7994,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>40</v>
       </c>
@@ -7979,7 +8017,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>40</v>
       </c>
@@ -8002,7 +8040,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>40</v>
       </c>
@@ -8025,7 +8063,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>40</v>
       </c>
@@ -8048,7 +8086,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>40</v>
       </c>
@@ -8072,6 +8110,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G300" xr:uid="{070FB04D-2C74-445D-8DA3-54633B601228}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8079,9 +8118,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FD9D45F-4E68-495E-84F9-17411AD946E6}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.7265625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -8107,7 +8156,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -8141,9 +8190,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D37599FE-85B8-4E48-8692-197E75CB900B}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -8163,7 +8212,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -8180,7 +8229,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -8197,7 +8246,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -8214,7 +8263,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -8231,7 +8280,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -8248,7 +8297,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -8265,7 +8314,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -8282,7 +8331,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -8299,7 +8348,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -8316,7 +8365,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -8333,7 +8382,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -8350,7 +8399,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -8367,7 +8416,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -8384,7 +8433,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -8401,7 +8450,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -8426,9 +8475,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68C4778F-5224-42D1-A755-DCA822844328}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>207</v>
       </c>
@@ -8442,7 +8494,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>208</v>
       </c>
@@ -8453,7 +8505,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>208</v>
       </c>
@@ -8464,7 +8516,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>208</v>
       </c>
@@ -8475,7 +8527,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>208</v>
       </c>
@@ -8486,7 +8538,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>208</v>
       </c>
@@ -8497,7 +8549,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>208</v>
       </c>
@@ -8508,7 +8560,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>208</v>
       </c>
@@ -8519,7 +8571,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>208</v>
       </c>
@@ -8530,7 +8582,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>209</v>
       </c>
@@ -8541,7 +8593,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>209</v>
       </c>
@@ -8552,7 +8604,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>209</v>
       </c>
@@ -8563,7 +8615,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>209</v>
       </c>
@@ -8574,7 +8626,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>209</v>
       </c>
@@ -8585,7 +8637,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>209</v>
       </c>
@@ -8596,7 +8648,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>209</v>
       </c>
@@ -8607,7 +8659,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>209</v>
       </c>
@@ -8618,7 +8670,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>210</v>
       </c>
@@ -8629,7 +8681,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>210</v>
       </c>
@@ -8640,7 +8692,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>210</v>
       </c>
@@ -8651,7 +8703,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>210</v>
       </c>
@@ -8662,7 +8714,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>210</v>
       </c>
@@ -8673,7 +8725,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>210</v>
       </c>
@@ -8684,7 +8736,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>210</v>
       </c>
@@ -8695,7 +8747,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>210</v>
       </c>
@@ -8713,10 +8765,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD2706A9-377C-41D4-A9A3-E473FB5F396C}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G553"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -8739,7 +8801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -8762,7 +8824,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -8785,7 +8847,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -8808,7 +8870,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -8831,7 +8893,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -8854,7 +8916,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -8877,7 +8939,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -8900,7 +8962,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -8923,7 +8985,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -8946,7 +9008,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -8969,7 +9031,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -8992,7 +9054,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -9015,7 +9077,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -9038,7 +9100,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -9061,7 +9123,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -9084,7 +9146,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -9107,7 +9169,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -9130,7 +9192,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -9153,7 +9215,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -9176,7 +9238,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -9199,7 +9261,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -9219,7 +9281,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -9239,7 +9301,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -9259,7 +9321,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -9279,7 +9341,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -9302,7 +9364,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -9325,7 +9387,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -9348,7 +9410,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -9371,7 +9433,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -9394,7 +9456,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -9417,7 +9479,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -9440,7 +9502,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -9463,7 +9525,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -9486,7 +9548,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -9509,7 +9571,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -9532,7 +9594,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -9555,7 +9617,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -9578,7 +9640,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -9601,7 +9663,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -9624,7 +9686,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -9647,7 +9709,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -9670,7 +9732,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>40</v>
       </c>
@@ -9693,7 +9755,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>40</v>
       </c>
@@ -9716,7 +9778,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>40</v>
       </c>
@@ -9739,7 +9801,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>40</v>
       </c>
@@ -9759,7 +9821,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>40</v>
       </c>
@@ -9779,7 +9841,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>40</v>
       </c>
@@ -9799,7 +9861,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>40</v>
       </c>
@@ -9819,7 +9881,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>40</v>
       </c>
@@ -9842,7 +9904,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>40</v>
       </c>
@@ -9865,7 +9927,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>40</v>
       </c>
@@ -9888,7 +9950,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>40</v>
       </c>
@@ -9911,7 +9973,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>40</v>
       </c>
@@ -9934,7 +9996,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>40</v>
       </c>
@@ -9957,7 +10019,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>40</v>
       </c>
@@ -9980,7 +10042,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>40</v>
       </c>
@@ -10003,7 +10065,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>40</v>
       </c>
@@ -10026,7 +10088,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>40</v>
       </c>
@@ -10049,7 +10111,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>40</v>
       </c>
@@ -10072,7 +10134,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>40</v>
       </c>
@@ -10095,7 +10157,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>40</v>
       </c>
@@ -10118,7 +10180,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>40</v>
       </c>
@@ -10141,7 +10203,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>40</v>
       </c>
@@ -10164,7 +10226,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>40</v>
       </c>
@@ -10187,7 +10249,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>40</v>
       </c>
@@ -10210,7 +10272,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>40</v>
       </c>
@@ -10233,7 +10295,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>40</v>
       </c>
@@ -10256,7 +10318,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>40</v>
       </c>
@@ -10279,7 +10341,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>40</v>
       </c>
@@ -10299,7 +10361,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>40</v>
       </c>
@@ -10319,7 +10381,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>40</v>
       </c>
@@ -10339,7 +10401,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>40</v>
       </c>
@@ -10359,7 +10421,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>40</v>
       </c>
@@ -10382,7 +10444,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>40</v>
       </c>
@@ -10405,7 +10467,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>40</v>
       </c>
@@ -10428,7 +10490,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>40</v>
       </c>
@@ -10451,7 +10513,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>40</v>
       </c>
@@ -10474,7 +10536,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>40</v>
       </c>
@@ -10497,7 +10559,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>40</v>
       </c>
@@ -10520,7 +10582,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>40</v>
       </c>
@@ -10543,7 +10605,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>40</v>
       </c>
@@ -10566,7 +10628,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>40</v>
       </c>
@@ -10589,7 +10651,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>40</v>
       </c>
@@ -10612,7 +10674,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>40</v>
       </c>
@@ -10635,7 +10697,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>40</v>
       </c>
@@ -10658,7 +10720,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>40</v>
       </c>
@@ -10681,7 +10743,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>40</v>
       </c>
@@ -10704,7 +10766,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>40</v>
       </c>
@@ -10727,7 +10789,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>40</v>
       </c>
@@ -10750,7 +10812,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>40</v>
       </c>
@@ -10773,7 +10835,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>40</v>
       </c>
@@ -10796,7 +10858,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>40</v>
       </c>
@@ -10819,7 +10881,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>40</v>
       </c>
@@ -10839,7 +10901,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>40</v>
       </c>
@@ -10859,7 +10921,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>40</v>
       </c>
@@ -10879,7 +10941,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>40</v>
       </c>
@@ -10899,7 +10961,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>40</v>
       </c>
@@ -10922,7 +10984,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>40</v>
       </c>
@@ -10945,7 +11007,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>40</v>
       </c>
@@ -10968,7 +11030,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>40</v>
       </c>
@@ -10991,7 +11053,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>40</v>
       </c>
@@ -11014,7 +11076,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>40</v>
       </c>
@@ -11037,7 +11099,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>40</v>
       </c>
@@ -11060,7 +11122,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>40</v>
       </c>
@@ -11083,7 +11145,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>40</v>
       </c>
@@ -11106,7 +11168,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>40</v>
       </c>
@@ -11129,7 +11191,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>40</v>
       </c>
@@ -11152,7 +11214,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>40</v>
       </c>
@@ -11175,7 +11237,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>40</v>
       </c>
@@ -11198,7 +11260,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>40</v>
       </c>
@@ -11221,7 +11283,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>40</v>
       </c>
@@ -11244,7 +11306,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>40</v>
       </c>
@@ -11267,7 +11329,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>40</v>
       </c>
@@ -11290,7 +11352,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>40</v>
       </c>
@@ -11313,7 +11375,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>40</v>
       </c>
@@ -11336,7 +11398,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>40</v>
       </c>
@@ -11359,7 +11421,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>40</v>
       </c>
@@ -11379,7 +11441,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>40</v>
       </c>
@@ -11399,7 +11461,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>40</v>
       </c>
@@ -11419,7 +11481,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>40</v>
       </c>
@@ -11439,7 +11501,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>40</v>
       </c>
@@ -11462,7 +11524,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>40</v>
       </c>
@@ -11485,7 +11547,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>40</v>
       </c>
@@ -11508,7 +11570,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>40</v>
       </c>
@@ -11531,7 +11593,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>40</v>
       </c>
@@ -11554,7 +11616,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>40</v>
       </c>
@@ -11577,7 +11639,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>40</v>
       </c>
@@ -11600,7 +11662,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>40</v>
       </c>
@@ -11623,7 +11685,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>40</v>
       </c>
@@ -11646,7 +11708,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>40</v>
       </c>
@@ -11669,7 +11731,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>40</v>
       </c>
@@ -11692,7 +11754,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>40</v>
       </c>
@@ -11715,7 +11777,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>40</v>
       </c>
@@ -11738,7 +11800,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>40</v>
       </c>
@@ -11761,7 +11823,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>40</v>
       </c>
@@ -11784,7 +11846,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>40</v>
       </c>
@@ -11807,7 +11869,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>40</v>
       </c>
@@ -11830,7 +11892,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>40</v>
       </c>
@@ -11853,7 +11915,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>40</v>
       </c>
@@ -11876,7 +11938,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>40</v>
       </c>
@@ -11899,7 +11961,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>40</v>
       </c>
@@ -11919,7 +11981,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>40</v>
       </c>
@@ -11939,7 +12001,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>40</v>
       </c>
@@ -11959,7 +12021,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>40</v>
       </c>
@@ -11979,7 +12041,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>40</v>
       </c>
@@ -12002,7 +12064,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>40</v>
       </c>
@@ -12025,7 +12087,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>40</v>
       </c>
@@ -12048,7 +12110,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>40</v>
       </c>
@@ -12071,7 +12133,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>40</v>
       </c>
@@ -12094,7 +12156,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>40</v>
       </c>
@@ -12117,7 +12179,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>40</v>
       </c>
@@ -12140,7 +12202,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>40</v>
       </c>
@@ -12163,7 +12225,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>40</v>
       </c>
@@ -12186,7 +12248,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>40</v>
       </c>
@@ -12209,7 +12271,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>40</v>
       </c>
@@ -12232,7 +12294,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>40</v>
       </c>
@@ -12255,7 +12317,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>40</v>
       </c>
@@ -12278,7 +12340,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>40</v>
       </c>
@@ -12301,7 +12363,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>40</v>
       </c>
@@ -12324,7 +12386,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>40</v>
       </c>
@@ -12347,7 +12409,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>40</v>
       </c>
@@ -12370,7 +12432,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>40</v>
       </c>
@@ -12393,7 +12455,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>40</v>
       </c>
@@ -12416,7 +12478,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>40</v>
       </c>
@@ -12439,7 +12501,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>40</v>
       </c>
@@ -12459,7 +12521,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>40</v>
       </c>
@@ -12479,7 +12541,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>40</v>
       </c>
@@ -12499,7 +12561,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>40</v>
       </c>
@@ -12519,7 +12581,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>40</v>
       </c>
@@ -12542,7 +12604,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>40</v>
       </c>
@@ -12565,7 +12627,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>40</v>
       </c>
@@ -12588,7 +12650,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>40</v>
       </c>
@@ -12611,7 +12673,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>40</v>
       </c>
@@ -12634,7 +12696,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>40</v>
       </c>
@@ -12657,7 +12719,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>40</v>
       </c>
@@ -12680,7 +12742,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>40</v>
       </c>
@@ -12703,7 +12765,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>40</v>
       </c>
@@ -12726,7 +12788,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>40</v>
       </c>
@@ -12749,7 +12811,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>40</v>
       </c>
@@ -12772,7 +12834,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>40</v>
       </c>
@@ -12795,7 +12857,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>40</v>
       </c>
@@ -12818,7 +12880,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>40</v>
       </c>
@@ -12841,7 +12903,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>40</v>
       </c>
@@ -12864,7 +12926,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>40</v>
       </c>
@@ -12887,7 +12949,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>40</v>
       </c>
@@ -12910,7 +12972,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>40</v>
       </c>
@@ -12933,7 +12995,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>40</v>
       </c>
@@ -12956,7 +13018,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>40</v>
       </c>
@@ -12979,7 +13041,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>40</v>
       </c>
@@ -12999,7 +13061,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>40</v>
       </c>
@@ -13019,7 +13081,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>40</v>
       </c>
@@ -13039,7 +13101,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>40</v>
       </c>
@@ -13059,7 +13121,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>40</v>
       </c>
@@ -13082,7 +13144,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>40</v>
       </c>
@@ -13105,7 +13167,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>40</v>
       </c>
@@ -13128,7 +13190,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>40</v>
       </c>
@@ -13151,7 +13213,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>40</v>
       </c>
@@ -13174,7 +13236,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>40</v>
       </c>
@@ -13197,7 +13259,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>40</v>
       </c>
@@ -13220,7 +13282,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>40</v>
       </c>
@@ -13243,7 +13305,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>40</v>
       </c>
@@ -13266,7 +13328,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>40</v>
       </c>
@@ -13289,7 +13351,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>40</v>
       </c>
@@ -13312,7 +13374,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>40</v>
       </c>
@@ -13335,7 +13397,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>40</v>
       </c>
@@ -13358,7 +13420,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>40</v>
       </c>
@@ -13381,7 +13443,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>40</v>
       </c>
@@ -13404,7 +13466,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>40</v>
       </c>
@@ -13427,7 +13489,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>40</v>
       </c>
@@ -13450,7 +13512,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>40</v>
       </c>
@@ -13473,7 +13535,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>40</v>
       </c>
@@ -13496,7 +13558,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>40</v>
       </c>
@@ -13519,7 +13581,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>40</v>
       </c>
@@ -13539,7 +13601,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>40</v>
       </c>
@@ -13559,7 +13621,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>40</v>
       </c>
@@ -13579,7 +13641,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>40</v>
       </c>
@@ -13599,7 +13661,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>40</v>
       </c>
@@ -13622,7 +13684,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>40</v>
       </c>
@@ -13645,7 +13707,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>40</v>
       </c>
@@ -13668,7 +13730,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>40</v>
       </c>
@@ -13691,7 +13753,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>40</v>
       </c>
@@ -13714,7 +13776,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>40</v>
       </c>
@@ -13737,7 +13799,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>40</v>
       </c>
@@ -13760,7 +13822,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>40</v>
       </c>
@@ -13783,7 +13845,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>40</v>
       </c>
@@ -13806,7 +13868,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>40</v>
       </c>
@@ -13829,7 +13891,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>40</v>
       </c>
@@ -13852,7 +13914,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>40</v>
       </c>
@@ -13875,7 +13937,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>40</v>
       </c>
@@ -13898,7 +13960,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>40</v>
       </c>
@@ -13921,7 +13983,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>40</v>
       </c>
@@ -13944,7 +14006,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>40</v>
       </c>
@@ -13967,7 +14029,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>40</v>
       </c>
@@ -13990,7 +14052,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>40</v>
       </c>
@@ -14013,7 +14075,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>40</v>
       </c>
@@ -14036,7 +14098,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>40</v>
       </c>
@@ -14059,7 +14121,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>40</v>
       </c>
@@ -14079,7 +14141,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>40</v>
       </c>
@@ -14099,7 +14161,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>40</v>
       </c>
@@ -14119,7 +14181,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>40</v>
       </c>
@@ -14139,7 +14201,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>40</v>
       </c>
@@ -14162,7 +14224,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>40</v>
       </c>
@@ -14185,7 +14247,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>40</v>
       </c>
@@ -14208,7 +14270,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>40</v>
       </c>
@@ -14231,7 +14293,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>40</v>
       </c>
@@ -14254,7 +14316,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>40</v>
       </c>
@@ -14277,7 +14339,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>40</v>
       </c>
@@ -14300,7 +14362,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>40</v>
       </c>
@@ -14323,7 +14385,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>40</v>
       </c>
@@ -14346,7 +14408,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>40</v>
       </c>
@@ -14369,7 +14431,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>40</v>
       </c>
@@ -14392,7 +14454,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>40</v>
       </c>
@@ -14415,7 +14477,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>40</v>
       </c>
@@ -14438,7 +14500,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>40</v>
       </c>
@@ -14461,7 +14523,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>40</v>
       </c>
@@ -14484,7 +14546,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>40</v>
       </c>
@@ -14507,7 +14569,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>40</v>
       </c>
@@ -14530,7 +14592,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>40</v>
       </c>
@@ -14553,7 +14615,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>40</v>
       </c>
@@ -14576,7 +14638,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>40</v>
       </c>
@@ -14599,7 +14661,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>40</v>
       </c>
@@ -14619,7 +14681,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>40</v>
       </c>
@@ -14639,7 +14701,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>40</v>
       </c>
@@ -14659,7 +14721,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>40</v>
       </c>
@@ -14679,7 +14741,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>40</v>
       </c>
@@ -14702,7 +14764,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>40</v>
       </c>
@@ -14725,7 +14787,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>40</v>
       </c>
@@ -14748,7 +14810,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>40</v>
       </c>
@@ -14771,7 +14833,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>40</v>
       </c>
@@ -14794,7 +14856,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>40</v>
       </c>
@@ -14817,7 +14879,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>40</v>
       </c>
@@ -14840,7 +14902,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>40</v>
       </c>
@@ -14863,7 +14925,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>40</v>
       </c>
@@ -14886,7 +14948,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>40</v>
       </c>
@@ -14909,7 +14971,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>40</v>
       </c>
@@ -14932,7 +14994,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>40</v>
       </c>
@@ -14955,7 +15017,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>40</v>
       </c>
@@ -14978,7 +15040,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>40</v>
       </c>
@@ -15001,7 +15063,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>40</v>
       </c>
@@ -15024,7 +15086,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>40</v>
       </c>
@@ -15047,7 +15109,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>40</v>
       </c>
@@ -15070,7 +15132,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>40</v>
       </c>
@@ -15093,7 +15155,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>40</v>
       </c>
@@ -15116,7 +15178,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>40</v>
       </c>
@@ -15139,7 +15201,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>40</v>
       </c>
@@ -15159,7 +15221,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>40</v>
       </c>
@@ -15179,7 +15241,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>40</v>
       </c>
@@ -15199,7 +15261,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>40</v>
       </c>
@@ -15219,7 +15281,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>40</v>
       </c>
@@ -15242,7 +15304,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>40</v>
       </c>
@@ -15265,7 +15327,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>40</v>
       </c>
@@ -15288,7 +15350,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>40</v>
       </c>
@@ -15311,7 +15373,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>40</v>
       </c>
@@ -15334,7 +15396,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>40</v>
       </c>
@@ -15357,7 +15419,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>40</v>
       </c>
@@ -15380,7 +15442,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>40</v>
       </c>
@@ -15403,7 +15465,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>40</v>
       </c>
@@ -15426,7 +15488,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>40</v>
       </c>
@@ -15449,7 +15511,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>40</v>
       </c>
@@ -15472,7 +15534,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>40</v>
       </c>
@@ -15495,7 +15557,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>40</v>
       </c>
@@ -15518,7 +15580,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>40</v>
       </c>
@@ -15541,7 +15603,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>40</v>
       </c>
@@ -15564,7 +15626,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>40</v>
       </c>
@@ -15587,7 +15649,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>40</v>
       </c>
@@ -15610,7 +15672,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>40</v>
       </c>
@@ -15633,7 +15695,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>40</v>
       </c>
@@ -15656,7 +15718,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>40</v>
       </c>
@@ -15679,7 +15741,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>40</v>
       </c>
@@ -15699,7 +15761,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>40</v>
       </c>
@@ -15719,7 +15781,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>40</v>
       </c>
@@ -15739,7 +15801,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>40</v>
       </c>
@@ -15759,7 +15821,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>40</v>
       </c>
@@ -15782,7 +15844,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>40</v>
       </c>
@@ -15805,7 +15867,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>40</v>
       </c>
@@ -15828,7 +15890,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>40</v>
       </c>
@@ -15851,7 +15913,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>40</v>
       </c>
@@ -15874,7 +15936,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>40</v>
       </c>
@@ -15897,7 +15959,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>40</v>
       </c>
@@ -15920,7 +15982,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>40</v>
       </c>
@@ -15943,7 +16005,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>40</v>
       </c>
@@ -15966,7 +16028,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>40</v>
       </c>
@@ -15989,7 +16051,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>40</v>
       </c>
@@ -16012,7 +16074,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>40</v>
       </c>
@@ -16035,7 +16097,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>40</v>
       </c>
@@ -16058,7 +16120,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>40</v>
       </c>
@@ -16081,7 +16143,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>40</v>
       </c>
@@ -16104,7 +16166,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>40</v>
       </c>
@@ -16127,7 +16189,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>40</v>
       </c>
@@ -16150,7 +16212,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>40</v>
       </c>
@@ -16173,7 +16235,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>40</v>
       </c>
@@ -16196,7 +16258,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>40</v>
       </c>
@@ -16219,7 +16281,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>40</v>
       </c>
@@ -16239,7 +16301,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>40</v>
       </c>
@@ -16259,7 +16321,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>40</v>
       </c>
@@ -16279,7 +16341,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>40</v>
       </c>
@@ -16299,7 +16361,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>40</v>
       </c>
@@ -16322,7 +16384,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>40</v>
       </c>
@@ -16345,7 +16407,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>40</v>
       </c>
@@ -16368,7 +16430,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>40</v>
       </c>
@@ -16391,7 +16453,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>40</v>
       </c>
@@ -16414,7 +16476,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>40</v>
       </c>
@@ -16437,7 +16499,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>40</v>
       </c>
@@ -16460,7 +16522,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>40</v>
       </c>
@@ -16483,7 +16545,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>40</v>
       </c>
@@ -16506,7 +16568,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>40</v>
       </c>
@@ -16529,7 +16591,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>40</v>
       </c>
@@ -16552,7 +16614,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>40</v>
       </c>
@@ -16575,7 +16637,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>40</v>
       </c>
@@ -16598,7 +16660,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>40</v>
       </c>
@@ -16621,7 +16683,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>40</v>
       </c>
@@ -16644,7 +16706,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>40</v>
       </c>
@@ -16667,7 +16729,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>40</v>
       </c>
@@ -16690,7 +16752,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>40</v>
       </c>
@@ -16713,7 +16775,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>40</v>
       </c>
@@ -16736,7 +16798,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>40</v>
       </c>
@@ -16759,7 +16821,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>40</v>
       </c>
@@ -16779,7 +16841,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>40</v>
       </c>
@@ -16799,7 +16861,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>40</v>
       </c>
@@ -16819,7 +16881,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>40</v>
       </c>
@@ -16839,7 +16901,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>40</v>
       </c>
@@ -16862,7 +16924,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>40</v>
       </c>
@@ -16885,7 +16947,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>40</v>
       </c>
@@ -16908,7 +16970,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>40</v>
       </c>
@@ -16931,7 +16993,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>40</v>
       </c>
@@ -16954,7 +17016,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>40</v>
       </c>
@@ -16977,7 +17039,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>40</v>
       </c>
@@ -17000,7 +17062,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>40</v>
       </c>
@@ -17023,7 +17085,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>40</v>
       </c>
@@ -17046,7 +17108,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>40</v>
       </c>
@@ -17069,7 +17131,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>40</v>
       </c>
@@ -17092,7 +17154,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>40</v>
       </c>
@@ -17115,7 +17177,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>40</v>
       </c>
@@ -17138,7 +17200,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>40</v>
       </c>
@@ -17161,7 +17223,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>40</v>
       </c>
@@ -17184,7 +17246,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>40</v>
       </c>
@@ -17207,7 +17269,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>40</v>
       </c>
@@ -17230,7 +17292,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>40</v>
       </c>
@@ -17253,7 +17315,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>40</v>
       </c>
@@ -17276,7 +17338,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>40</v>
       </c>
@@ -17299,7 +17361,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>40</v>
       </c>
@@ -17319,7 +17381,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>40</v>
       </c>
@@ -17339,7 +17401,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>40</v>
       </c>
@@ -17359,7 +17421,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>40</v>
       </c>
@@ -17379,7 +17441,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>40</v>
       </c>
@@ -17402,7 +17464,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>40</v>
       </c>
@@ -17425,7 +17487,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>40</v>
       </c>
@@ -17448,7 +17510,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>40</v>
       </c>
@@ -17471,7 +17533,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>40</v>
       </c>
@@ -17494,7 +17556,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>40</v>
       </c>
@@ -17517,7 +17579,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>40</v>
       </c>
@@ -17540,7 +17602,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>40</v>
       </c>
@@ -17563,7 +17625,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>40</v>
       </c>
@@ -17586,7 +17648,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>40</v>
       </c>
@@ -17609,7 +17671,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>40</v>
       </c>
@@ -17632,7 +17694,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>40</v>
       </c>
@@ -17655,7 +17717,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>40</v>
       </c>
@@ -17678,7 +17740,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>40</v>
       </c>
@@ -17701,7 +17763,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>40</v>
       </c>
@@ -17724,7 +17786,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>40</v>
       </c>
@@ -17747,7 +17809,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>40</v>
       </c>
@@ -17770,7 +17832,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>40</v>
       </c>
@@ -17793,7 +17855,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>40</v>
       </c>
@@ -17816,7 +17878,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>40</v>
       </c>
@@ -17839,7 +17901,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>40</v>
       </c>
@@ -17859,7 +17921,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>40</v>
       </c>
@@ -17879,7 +17941,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>40</v>
       </c>
@@ -17899,7 +17961,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>40</v>
       </c>
@@ -17919,7 +17981,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>40</v>
       </c>
@@ -17942,7 +18004,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>40</v>
       </c>
@@ -17965,7 +18027,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>40</v>
       </c>
@@ -17988,7 +18050,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>40</v>
       </c>
@@ -18011,7 +18073,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>40</v>
       </c>
@@ -18034,7 +18096,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>40</v>
       </c>
@@ -18057,7 +18119,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>40</v>
       </c>
@@ -18080,7 +18142,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>40</v>
       </c>
@@ -18103,7 +18165,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>40</v>
       </c>
@@ -18126,7 +18188,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>40</v>
       </c>
@@ -18149,7 +18211,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>40</v>
       </c>
@@ -18172,7 +18234,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>40</v>
       </c>
@@ -18195,7 +18257,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>40</v>
       </c>
@@ -18218,7 +18280,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>40</v>
       </c>
@@ -18241,7 +18303,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>40</v>
       </c>
@@ -18264,7 +18326,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>40</v>
       </c>
@@ -18287,7 +18349,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
         <v>40</v>
       </c>
@@ -18310,7 +18372,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>40</v>
       </c>
@@ -18333,7 +18395,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>40</v>
       </c>
@@ -18356,7 +18418,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>40</v>
       </c>
@@ -18379,7 +18441,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>40</v>
       </c>
@@ -18399,7 +18461,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>40</v>
       </c>
@@ -18419,7 +18481,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>40</v>
       </c>
@@ -18439,7 +18501,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>40</v>
       </c>
@@ -18459,7 +18521,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>40</v>
       </c>
@@ -18482,7 +18544,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>40</v>
       </c>
@@ -18505,7 +18567,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>40</v>
       </c>
@@ -18528,7 +18590,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>40</v>
       </c>
@@ -18551,7 +18613,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>40</v>
       </c>
@@ -18574,7 +18636,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>40</v>
       </c>
@@ -18597,7 +18659,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
         <v>40</v>
       </c>
@@ -18620,7 +18682,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>40</v>
       </c>
@@ -18643,7 +18705,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>40</v>
       </c>
@@ -18666,7 +18728,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>40</v>
       </c>
@@ -18689,7 +18751,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>40</v>
       </c>
@@ -18712,7 +18774,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>40</v>
       </c>
@@ -18735,7 +18797,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>40</v>
       </c>
@@ -18758,7 +18820,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>40</v>
       </c>
@@ -18781,7 +18843,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>40</v>
       </c>
@@ -18804,7 +18866,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>40</v>
       </c>
@@ -18827,7 +18889,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>40</v>
       </c>
@@ -18850,7 +18912,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>40</v>
       </c>
@@ -18873,7 +18935,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>40</v>
       </c>
@@ -18896,7 +18958,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>40</v>
       </c>
@@ -18919,7 +18981,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>40</v>
       </c>
@@ -18939,7 +19001,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>40</v>
       </c>
@@ -18959,7 +19021,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
         <v>40</v>
       </c>
@@ -18979,7 +19041,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>40</v>
       </c>
@@ -18999,7 +19061,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>40</v>
       </c>
@@ -19022,7 +19084,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>40</v>
       </c>
@@ -19045,7 +19107,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>40</v>
       </c>
@@ -19068,7 +19130,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>40</v>
       </c>
@@ -19091,7 +19153,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>40</v>
       </c>
@@ -19114,7 +19176,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>40</v>
       </c>
@@ -19137,7 +19199,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>40</v>
       </c>
@@ -19160,7 +19222,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>40</v>
       </c>
@@ -19183,7 +19245,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>40</v>
       </c>
@@ -19206,7 +19268,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>40</v>
       </c>
@@ -19229,7 +19291,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>40</v>
       </c>
@@ -19252,7 +19314,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>40</v>
       </c>
@@ -19275,7 +19337,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>40</v>
       </c>
@@ -19298,7 +19360,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>40</v>
       </c>
@@ -19321,7 +19383,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>40</v>
       </c>
@@ -19344,7 +19406,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>40</v>
       </c>
@@ -19367,7 +19429,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>40</v>
       </c>
@@ -19390,7 +19452,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>40</v>
       </c>
@@ -19413,7 +19475,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>40</v>
       </c>
@@ -19436,7 +19498,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>40</v>
       </c>
@@ -19459,7 +19521,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>40</v>
       </c>
@@ -19479,7 +19541,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>40</v>
       </c>
@@ -19499,7 +19561,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>40</v>
       </c>
@@ -19519,7 +19581,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
         <v>40</v>
       </c>
@@ -19539,7 +19601,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
         <v>40</v>
       </c>
@@ -19562,7 +19624,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
         <v>40</v>
       </c>
@@ -19585,7 +19647,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
         <v>40</v>
       </c>
@@ -19608,7 +19670,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
         <v>40</v>
       </c>
@@ -19631,7 +19693,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>40</v>
       </c>
@@ -19654,7 +19716,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>40</v>
       </c>
@@ -19677,7 +19739,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>40</v>
       </c>
@@ -19700,7 +19762,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>40</v>
       </c>
@@ -19723,7 +19785,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>40</v>
       </c>
@@ -19746,7 +19808,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>40</v>
       </c>
@@ -19769,7 +19831,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
         <v>40</v>
       </c>
@@ -19792,7 +19854,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
         <v>40</v>
       </c>
@@ -19815,7 +19877,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
         <v>40</v>
       </c>
@@ -19838,7 +19900,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>40</v>
       </c>
@@ -19861,7 +19923,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>40</v>
       </c>
@@ -19884,7 +19946,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
         <v>40</v>
       </c>
@@ -19907,7 +19969,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>40</v>
       </c>
@@ -19930,7 +19992,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>40</v>
       </c>
@@ -19953,7 +20015,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>40</v>
       </c>
@@ -19976,7 +20038,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>40</v>
       </c>
@@ -19999,7 +20061,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>40</v>
       </c>
@@ -20019,7 +20081,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>40</v>
       </c>
@@ -20039,7 +20101,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
         <v>40</v>
       </c>
@@ -20059,7 +20121,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
         <v>40</v>
       </c>
@@ -20079,7 +20141,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
         <v>40</v>
       </c>
@@ -20102,7 +20164,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
         <v>40</v>
       </c>
@@ -20125,7 +20187,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
         <v>40</v>
       </c>
@@ -20148,7 +20210,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
         <v>40</v>
       </c>
@@ -20171,7 +20233,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
         <v>40</v>
       </c>
@@ -20194,7 +20256,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>40</v>
       </c>
@@ -20217,7 +20279,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>40</v>
       </c>
@@ -20240,7 +20302,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>40</v>
       </c>
@@ -20263,7 +20325,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>40</v>
       </c>
@@ -20286,7 +20348,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
         <v>40</v>
       </c>
@@ -20309,7 +20371,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
         <v>40</v>
       </c>
@@ -20332,7 +20394,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>40</v>
       </c>
@@ -20355,7 +20417,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>40</v>
       </c>
@@ -20378,7 +20440,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>40</v>
       </c>
@@ -20401,7 +20463,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>40</v>
       </c>
@@ -20424,7 +20486,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>40</v>
       </c>
@@ -20447,7 +20509,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
         <v>40</v>
       </c>
@@ -20470,7 +20532,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>40</v>
       </c>
@@ -20493,7 +20555,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>40</v>
       </c>
@@ -20516,7 +20578,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>40</v>
       </c>
@@ -20539,7 +20601,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>40</v>
       </c>
@@ -20559,7 +20621,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>40</v>
       </c>
@@ -20579,7 +20641,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>40</v>
       </c>
@@ -20599,7 +20661,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>40</v>
       </c>
@@ -20619,7 +20681,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
         <v>40</v>
       </c>
@@ -20642,7 +20704,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
         <v>40</v>
       </c>
@@ -20665,7 +20727,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
         <v>40</v>
       </c>
@@ -20688,7 +20750,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
         <v>40</v>
       </c>
@@ -20711,7 +20773,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
         <v>40</v>
       </c>
@@ -20734,7 +20796,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
         <v>40</v>
       </c>
@@ -20757,7 +20819,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
         <v>40</v>
       </c>
@@ -20780,7 +20842,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
         <v>40</v>
       </c>
@@ -20803,7 +20865,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
         <v>40</v>
       </c>
@@ -20826,7 +20888,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
         <v>40</v>
       </c>
@@ -20849,7 +20911,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
         <v>40</v>
       </c>
@@ -20872,7 +20934,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
         <v>40</v>
       </c>
@@ -20895,7 +20957,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
         <v>40</v>
       </c>
@@ -20918,7 +20980,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
         <v>40</v>
       </c>
@@ -20941,7 +21003,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
         <v>40</v>
       </c>
@@ -20964,7 +21026,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>40</v>
       </c>
@@ -20987,7 +21049,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
         <v>40</v>
       </c>
@@ -21010,7 +21072,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>40</v>
       </c>
@@ -21033,7 +21095,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>40</v>
       </c>
@@ -21056,7 +21118,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>40</v>
       </c>
@@ -21079,7 +21141,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
         <v>40</v>
       </c>
@@ -21099,7 +21161,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
         <v>40</v>
       </c>
@@ -21119,7 +21181,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
         <v>40</v>
       </c>
@@ -21139,7 +21201,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
         <v>40</v>
       </c>
@@ -21160,6 +21222,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G553" xr:uid="{CD2706A9-377C-41D4-A9A3-E473FB5F396C}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="CdTe 2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -21167,9 +21236,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF11F923-AAF7-4ED6-A47D-7647C9BA8BB7}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -21186,7 +21261,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -21200,7 +21275,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -21214,7 +21289,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -21228,7 +21303,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -21242,7 +21317,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -21256,7 +21331,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -21270,7 +21345,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -21284,7 +21359,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -21298,7 +21373,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -21312,7 +21387,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -21326,7 +21401,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -21340,7 +21415,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -21362,14 +21437,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B490D8CD-E455-4024-A4A5-0FF6A3A9C116}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -21383,7 +21458,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -21394,7 +21469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -21405,7 +21480,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -21416,7 +21491,7 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -21427,7 +21502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -21438,7 +21513,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -21449,7 +21524,7 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -21460,7 +21535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -21471,7 +21546,7 @@
         <v>2500000</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -21482,7 +21557,7 @@
         <v>4500000</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -21493,7 +21568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -21504,7 +21579,7 @@
         <v>1500000</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -21515,7 +21590,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -21526,7 +21601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -21537,7 +21612,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -21548,7 +21623,7 @@
         <v>6000000</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -21559,7 +21634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -21570,7 +21645,7 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -21581,7 +21656,7 @@
         <v>7500000</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -21592,7 +21667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -21603,7 +21678,7 @@
         <v>7500000</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -21614,7 +21689,7 @@
         <v>9500000</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -21625,7 +21700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -21636,7 +21711,7 @@
         <v>3500000</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -21650,4 +21725,196 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B26C7F3-AF79-4DB6-B81F-42616D380E1F}">
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="162.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>288</v>
+      </c>
+      <c r="C11" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C13" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C14" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C15" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C16" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{95965d95-ecc0-4720-b759-1f33c42ed7da}" enabled="1" method="Standard" siteId="{a0f29d7e-28cd-4f54-8442-7885aee7c080}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>